--- a/data/run_dry.xlsx
+++ b/data/run_dry.xlsx
@@ -524,10 +524,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1002.313595775</v>
+        <v>1002.008263876225</v>
       </c>
       <c r="H2" t="n">
-        <v>1.401326201279921</v>
+        <v>1.401497593358524</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,29 +559,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153.71851360446</v>
+        <v>153.8821471640656</v>
       </c>
       <c r="C3" t="n">
-        <v>1148.197074234486</v>
+        <v>1218.597577512264</v>
       </c>
       <c r="D3" t="n">
         <v>163468.0278</v>
       </c>
       <c r="E3" t="n">
-        <v>1029771.090250331</v>
+        <v>1074117.508714112</v>
       </c>
       <c r="F3" t="n">
-        <v>1503.273234344108</v>
+        <v>1483.929206040197</v>
       </c>
       <c r="G3" t="n">
-        <v>1243.150389587259</v>
+        <v>1268.642823336422</v>
       </c>
       <c r="H3" t="n">
-        <v>1.300233882129428</v>
+        <v>1.292436642229587</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>products</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>860.0470742344856</v>
+        <v>930.4475775122643</v>
       </c>
       <c r="L3" t="n">
         <v>63156.27779999998</v>
       </c>
       <c r="M3" t="n">
-        <v>1029771.090250331</v>
+        <v>1074117.508714112</v>
       </c>
       <c r="N3" t="n">
-        <v>1500.388256592897</v>
+        <v>1481.044228288985</v>
       </c>
     </row>
     <row r="4">
@@ -609,29 +609,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.71851360446</v>
+        <v>153.8821471640656</v>
       </c>
       <c r="C4" t="n">
-        <v>1148.197074234486</v>
+        <v>1218.597577512264</v>
       </c>
       <c r="D4" t="n">
         <v>160198.667244</v>
       </c>
       <c r="E4" t="n">
-        <v>1029771.090250331</v>
+        <v>1074117.508714112</v>
       </c>
       <c r="F4" t="n">
-        <v>1509.072479461372</v>
+        <v>1489.728451157461</v>
       </c>
       <c r="G4" t="n">
-        <v>1243.150389587259</v>
+        <v>1268.642823336422</v>
       </c>
       <c r="H4" t="n">
-        <v>1.300233882129428</v>
+        <v>1.292436642229587</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>products</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>860.0470742344856</v>
+        <v>930.4475775122643</v>
       </c>
       <c r="L4" t="n">
         <v>59886.91724399998</v>
       </c>
       <c r="M4" t="n">
-        <v>1029771.090250331</v>
+        <v>1074117.508714112</v>
       </c>
       <c r="N4" t="n">
-        <v>1506.187501710161</v>
+        <v>1486.843473406249</v>
       </c>
     </row>
     <row r="5">
@@ -674,10 +674,10 @@
         <v>2.884977751211491</v>
       </c>
       <c r="G5" t="n">
-        <v>1002.313595775</v>
+        <v>1002.008263876225</v>
       </c>
       <c r="H5" t="n">
-        <v>1.401326201279921</v>
+        <v>1.401497593358524</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -712,22 +712,22 @@
         <v>150</v>
       </c>
       <c r="C6" t="n">
-        <v>344.2642809823155</v>
+        <v>344.2001828923821</v>
       </c>
       <c r="D6" t="n">
         <v>175545.5625</v>
       </c>
       <c r="E6" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="F6" t="n">
-        <v>21.06954575697489</v>
+        <v>21.07179320572104</v>
       </c>
       <c r="G6" t="n">
-        <v>1007.906834832523</v>
+        <v>1010.546900773356</v>
       </c>
       <c r="H6" t="n">
-        <v>1.39821223715776</v>
+        <v>1.396759140767428</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>56.11428098231556</v>
+        <v>56.05018289238217</v>
       </c>
       <c r="L6" t="n">
         <v>75233.8125</v>
       </c>
       <c r="M6" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="N6" t="n">
-        <v>18.1845680057634</v>
+        <v>18.18681545450955</v>
       </c>
     </row>
     <row r="7">
@@ -762,22 +762,22 @@
         <v>95.54140127388536</v>
       </c>
       <c r="C7" t="n">
-        <v>369.9003821238875</v>
+        <v>369.7427185252309</v>
       </c>
       <c r="D7" t="n">
         <v>217237.63359375</v>
       </c>
       <c r="E7" t="n">
-        <v>82272.64649599389</v>
+        <v>82263.03495465945</v>
       </c>
       <c r="F7" t="n">
-        <v>32.38255185846904</v>
+        <v>32.38585990705198</v>
       </c>
       <c r="G7" t="n">
-        <v>1010.441177578178</v>
+        <v>1014.641848080168</v>
       </c>
       <c r="H7" t="n">
-        <v>1.396817127112574</v>
+        <v>1.394526138586409</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>81.75038212388756</v>
+        <v>81.59271852523091</v>
       </c>
       <c r="L7" t="n">
         <v>116925.88359375</v>
       </c>
       <c r="M7" t="n">
-        <v>82272.64649599389</v>
+        <v>82263.03495465945</v>
       </c>
       <c r="N7" t="n">
-        <v>29.49757410725755</v>
+        <v>29.50088215584049</v>
       </c>
     </row>
     <row r="8">
@@ -812,22 +812,22 @@
         <v>95.54140127388536</v>
       </c>
       <c r="C8" t="n">
-        <v>815.8121138811111</v>
+        <v>803.8048967719078</v>
       </c>
       <c r="D8" t="n">
         <v>2752835.2929</v>
       </c>
       <c r="E8" t="n">
-        <v>542347.5496748937</v>
+        <v>539871.1285909641</v>
       </c>
       <c r="F8" t="n">
-        <v>117.3447796517406</v>
+        <v>118.029702934405</v>
       </c>
       <c r="G8" t="n">
-        <v>1052.420590019846</v>
+        <v>1096.759689707324</v>
       </c>
       <c r="H8" t="n">
-        <v>1.375052229786431</v>
+        <v>1.354514576157032</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>527.6621138811112</v>
+        <v>515.6548967719078</v>
       </c>
       <c r="L8" t="n">
         <v>2652523.5429</v>
       </c>
       <c r="M8" t="n">
-        <v>542347.5496748937</v>
+        <v>539871.1285909641</v>
       </c>
       <c r="N8" t="n">
-        <v>114.4598019005291</v>
+        <v>115.1447251831935</v>
       </c>
     </row>
     <row r="9">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99.25991487834534</v>
+        <v>99.42354843795094</v>
       </c>
       <c r="C9" t="n">
         <v>2000</v>
@@ -868,16 +868,16 @@
         <v>2587665.175326</v>
       </c>
       <c r="E9" t="n">
-        <v>2122367.005288256</v>
+        <v>2186801.328024609</v>
       </c>
       <c r="F9" t="n">
-        <v>1420.358005319736</v>
+        <v>1418.294621658791</v>
       </c>
       <c r="G9" t="n">
-        <v>1319.32</v>
+        <v>1426</v>
       </c>
       <c r="H9" t="n">
-        <v>1.278080025661575</v>
+        <v>1.252033533812935</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -896,10 +896,10 @@
         <v>2487353.425326</v>
       </c>
       <c r="M9" t="n">
-        <v>2122367.005288256</v>
+        <v>2186801.328024609</v>
       </c>
       <c r="N9" t="n">
-        <v>1417.473027568525</v>
+        <v>1415.40964390758</v>
       </c>
     </row>
     <row r="10">
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99.25991487834534</v>
+        <v>99.42354843795094</v>
       </c>
       <c r="C10" t="n">
-        <v>1657.305115461349</v>
+        <v>1685.180482268333</v>
       </c>
       <c r="D10" t="n">
-        <v>978845.1111495176</v>
+        <v>994344.9201061744</v>
       </c>
       <c r="E10" t="n">
-        <v>1675054.420336681</v>
+        <v>1742619.608617999</v>
       </c>
       <c r="F10" t="n">
-        <v>1454.156749698699</v>
+        <v>1451.260051886896</v>
       </c>
       <c r="G10" t="n">
-        <v>1290.769287737871</v>
+        <v>1393.827051266041</v>
       </c>
       <c r="H10" t="n">
-        <v>1.285990011647858</v>
+        <v>1.259359926224191</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1369.155115461349</v>
+        <v>1397.030482268333</v>
       </c>
       <c r="L10" t="n">
-        <v>878533.3611495176</v>
+        <v>894033.1701061744</v>
       </c>
       <c r="M10" t="n">
-        <v>1675054.420336681</v>
+        <v>1742619.608617999</v>
       </c>
       <c r="N10" t="n">
-        <v>1451.271771947488</v>
+        <v>1448.375074135685</v>
       </c>
     </row>
     <row r="11">
@@ -959,25 +959,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99.25991487834534</v>
+        <v>99.42354843795094</v>
       </c>
       <c r="C11" t="n">
-        <v>1570.863124728203</v>
+        <v>1605.215865373611</v>
       </c>
       <c r="D11" t="n">
-        <v>751254.4250182046</v>
+        <v>767386.5531834213</v>
       </c>
       <c r="E11" t="n">
-        <v>1563806.970994971</v>
+        <v>1631566.024421179</v>
       </c>
       <c r="F11" t="n">
-        <v>1461.180073031861</v>
+        <v>1458.119427873348</v>
       </c>
       <c r="G11" t="n">
-        <v>1283.122457985857</v>
+        <v>1383.585845251684</v>
       </c>
       <c r="H11" t="n">
-        <v>1.288185557979385</v>
+        <v>1.261782250491932</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1282.713124728203</v>
+        <v>1317.065865373611</v>
       </c>
       <c r="L11" t="n">
-        <v>650942.6750182046</v>
+        <v>667074.8031834213</v>
       </c>
       <c r="M11" t="n">
-        <v>1563806.970994971</v>
+        <v>1631566.024421179</v>
       </c>
       <c r="N11" t="n">
-        <v>1458.29509528065</v>
+        <v>1455.234450122137</v>
       </c>
     </row>
     <row r="12">
@@ -1012,22 +1012,22 @@
         <v>54.45859872611464</v>
       </c>
       <c r="C12" t="n">
-        <v>344.2642809823155</v>
+        <v>344.2001828923821</v>
       </c>
       <c r="D12" t="n">
         <v>168523.74</v>
       </c>
       <c r="E12" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="F12" t="n">
-        <v>32.78761644313835</v>
+        <v>32.78986389188449</v>
       </c>
       <c r="G12" t="n">
-        <v>1007.906834832523</v>
+        <v>1010.546900773356</v>
       </c>
       <c r="H12" t="n">
-        <v>1.39821223715776</v>
+        <v>1.396759140767428</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>56.11428098231556</v>
+        <v>56.05018289238217</v>
       </c>
       <c r="L12" t="n">
         <v>68211.98999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="N12" t="n">
-        <v>29.90263869192686</v>
+        <v>29.904886140673</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81457.61150583666</v>
+        <v>84050.90854260385</v>
       </c>
     </row>
     <row r="3">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81457.61150583666</v>
+        <v>84050.90854260385</v>
       </c>
     </row>
     <row r="4">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8621070487758792</v>
+        <v>0.864236309924288</v>
       </c>
     </row>
     <row r="5">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>543.0507433722444</v>
+        <v>879.7328427459203</v>
       </c>
     </row>
     <row r="6">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.564967638651588e-05</v>
+        <v>4.618804521426192e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1135,97 +1135,107 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>529.9141241738977</v>
+        <v>546.2031177209313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_fan_W</t>
+          <t>V_freestream_mps</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8460199.729024339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_hpc_W</t>
+          <t>W_fan_W</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43956200.94065922</v>
+        <v>8459859.852200732</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_lpc_W</t>
+          <t>W_hpc_W</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2471781.684952066</v>
+        <v>43720518.50028389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>choked</t>
+          <t>W_lpc_W</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2471079.866877826</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f_main</t>
+          <t>choked</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03892044239334775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>m_fuel_kgps</t>
+          <t>f_main</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.718513604459976</v>
+        <v>0.04063314031721973</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pe_exit_Pa</t>
+          <t>m_fuel_kgps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>101324.9999996147</v>
+        <v>3.88214716406558</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>w_hpt_Jpkg</t>
+          <t>pe_exit_Pa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>447312.5231346461</v>
+        <v>101325.0000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>w_hpt_Jpkg</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>444181.8924501344</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>w_lpt_Jpkg</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>111247.379994198</v>
+      <c r="B17" t="n">
+        <v>111053.7033234665</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1267,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tt4</t>
+          <t>TIT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1327,7 +1337,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eta_burner</t>
+          <t>diffuser_pr</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1337,121 +1347,121 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eta_fan</t>
+          <t>eta_burner</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eta_hpc</t>
+          <t>eta_fan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eta_hpt</t>
+          <t>eta_hpc</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eta_lpc</t>
+          <t>eta_hpt</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eta_lpt</t>
+          <t>eta_lpc</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eta_mech</t>
+          <t>eta_lpt</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eta_nozzle</t>
+          <t>eta_mech</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fan_pr</t>
+          <t>eta_nozzle</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.75</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fuel_LHV</t>
+          <t>fan_pr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43150000</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hpc_duct_pr</t>
+          <t>fuel_LHV</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.99</v>
+        <v>43150000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hpc_pr</t>
+          <t>hpc_duct_pr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12.8</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inlet_pr</t>
+          <t>hpc_pr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.99</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="22">
